--- a/PsychoPy/Intro1_pic.xlsx
+++ b/PsychoPy/Intro1_pic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iowa-my.sharepoint.com/personal/markberardi_uiowa_edu/Documents/Documents/GitHub/VLT_LITE/PsychoPy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iowa-my.sharepoint.com/personal/markberardi_uiowa_edu/Documents/Documents/GitHub/VLT-VBAL/PsychoPy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{3F4EA370-E97A-4F84-B487-3AE987A0CC3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98FC6373-ED32-4842-AECE-F941FC3BF1F5}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{3F4EA370-E97A-4F84-B487-3AE987A0CC3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40208CD6-0B9A-497E-807B-3E896BE34821}"/>
   <bookViews>
-    <workbookView xWindow="19103" yWindow="5573" windowWidth="21794" windowHeight="13874" xr2:uid="{212967D1-BA53-44B9-9773-6E730732E7A3}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{212967D1-BA53-44B9-9773-6E730732E7A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>IntroText</t>
   </si>
@@ -44,22 +44,16 @@
     <t>IntroWav</t>
   </si>
   <si>
-    <t>Welcome to the study. Please click anywhere to continue.</t>
-  </si>
-  <si>
-    <t>Intro1A.wav</t>
-  </si>
-  <si>
     <t>First, here is an example.</t>
   </si>
   <si>
-    <t>Intro1C.wav</t>
-  </si>
-  <si>
-    <t>Intro1B_pic.wav</t>
-  </si>
-  <si>
-    <t>In this study, you will narrate stories from a children's picture book.</t>
+    <t>Intro1_pic.wav</t>
+  </si>
+  <si>
+    <t>Intro2_pic.wav</t>
+  </si>
+  <si>
+    <t>Next in this study, you will narrate stories from a children's picture book.</t>
   </si>
 </sst>
 </file>
@@ -414,13 +408,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2E6258A-B145-455A-AC2A-2B24E0AA2D8C}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -428,28 +422,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
